--- a/project-a/tables/excel/StatTable.xlsx
+++ b/project-a/tables/excel/StatTable.xlsx
@@ -414,15 +414,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -434,30 +435,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>character</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>level</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>attack_power</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>defense_power</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>max_hp</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>crit_rate</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>crit_damage</t>
         </is>
@@ -466,30 +472,35 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>key,int</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -526,144 +537,184 @@
           <t>data</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>160</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>45</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>90</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.03</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>10</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>195</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>58</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>131</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.03</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>249</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>77</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>180</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>0.03</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>30</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>304</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>97</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>229</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.03</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>40</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>358</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>116</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>278</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.03</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>50</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>413</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>136</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>327</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>0.03</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>tsuki</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>60</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>467</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>155</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>376</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.03</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.25</v>
       </c>
     </row>

--- a/project-a/tables/excel/StatTable.xlsx
+++ b/project-a/tables/excel/StatTable.xlsx
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>800</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>160</v>
+        <v>2500</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>

--- a/project-a/tables/excel/StatTable.xlsx
+++ b/project-a/tables/excel/StatTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="player_growth" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="monster_stats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_growth" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_stats" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Abyssal Crown Guardian</t>
+          <t>심연 왕관 수호자</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -876,7 +876,7 @@
         <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bog Stalker</t>
+          <t>늪 추적자</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -903,7 +903,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mire Imp</t>
+          <t>마이어 임프</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -930,7 +930,7 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bone Crawler</t>
+          <t>뼈 크롤러</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -957,7 +957,7 @@
         <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Crown Acolyte</t>
+          <t>왕관 시종</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -984,7 +984,7 @@
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frost Revenant</t>
+          <t>프로스트 레버넌트</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1011,7 +1011,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gravebound Crawler</t>
+          <t>무덤 크롤러</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1038,7 +1038,7 @@
         <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Training Goblin</t>
+          <t>훈련 고블린</t>
         </is>
       </c>
       <c r="D12" t="n">

--- a/project-a/tables/excel/StatTable.xlsx
+++ b/project-a/tables/excel/StatTable.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_growth" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monster_stats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlayerGrowth" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterStats" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,42 +430,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>#data</t>
+          <t>#archive</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>attack_power</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>defense_power</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>max_hp</t>
+          <t>MaxHp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>crit_rate</t>
+          <t>CritRate</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>crit_damage</t>
+          <t>CritDamage</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -571,7 +571,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -596,7 +596,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -621,7 +621,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -646,7 +646,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -671,7 +671,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -696,7 +696,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>tsuki</t>
+          <t>Tsuki</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -750,37 +750,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>display_name</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>max_hp</t>
+          <t>MaxHp</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>attack_power</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>defense_power</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>crit_rate</t>
+          <t>CritRate</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>crit_damage</t>
+          <t>CritDamage</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>abyssal_crown_guardian</t>
+          <t>AbyssalCrownGuardian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>bog_stalker</t>
+          <t>BogStalker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>mire_imp</t>
+          <t>MireImp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>bone_crawler</t>
+          <t>BoneCrawler</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>crown_acolyte</t>
+          <t>CrownAcolyte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>frost_revenant</t>
+          <t>FrostRevenant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1023,7 +1023,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>gravebound_crawler</t>
+          <t>GraveboundCrawler</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1050,7 +1050,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>monster_dummy</t>
+          <t>MonsterDummy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">

--- a/project-a/tables/excel/StatTable.xlsx
+++ b/project-a/tables/excel/StatTable.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A2:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -426,7 +426,6 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -559,7 +558,7 @@
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G5" t="n">
         <v>0.03</v>
@@ -729,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A2:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -741,7 +740,6 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
